--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512462_ELIMINGRA14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512462_ELIMINGRA14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6069</v>
+        <v>9.352499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8941</v>
+        <v>5.1541</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7128</v>
+        <v>4.1984</v>
       </c>
       <c r="G2" t="n">
-        <v>7.2914</v>
+        <v>7.3057</v>
       </c>
       <c r="H2" t="n">
-        <v>6.311</v>
+        <v>6.3528</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9804</v>
+        <v>0.953</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9583</v>
+        <v>6.1148</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7984</v>
+        <v>5.9526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3331</v>
+        <v>1.191</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.4001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8205</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5752</v>
+        <v>1.3262</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0166</v>
+        <v>1.0383</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5586</v>
+        <v>0.2879</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7597</v>
+        <v>4.5784</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5848</v>
+        <v>5.5142</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-0.9358</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9231</v>
+        <v>4.0363</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3861</v>
+        <v>0.4342</v>
       </c>
       <c r="I3" t="n">
-        <v>3.537</v>
+        <v>3.6021</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5322</v>
+        <v>4.7979</v>
       </c>
       <c r="K3" t="n">
-        <v>0.887</v>
+        <v>1.0367</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6452</v>
+        <v>3.7612</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6091</v>
+        <v>-0.7617</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5009</v>
+        <v>-0.6025</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3034</v>
+        <v>-0.5941</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.2215</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9571</v>
+        <v>-0.8157</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6035</v>
+        <v>4.2588</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2552</v>
+        <v>1.3572</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3483</v>
+        <v>2.9016</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7667</v>
+        <v>2.5687</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2645</v>
+        <v>2.2475</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5023</v>
+        <v>0.3212</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9048</v>
+        <v>2.2423</v>
       </c>
       <c r="K4" t="n">
-        <v>2.901</v>
+        <v>1.6421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0038</v>
+        <v>0.6002</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8619</v>
+        <v>0.3265</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6365</v>
+        <v>0.6054</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4985</v>
+        <v>-0.2789</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0003</v>
+        <v>1.7526</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0006</v>
+        <v>2.7263</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5637</v>
+        <v>-0.0625</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.509</v>
+        <v>0.0886</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0547</v>
+        <v>-0.1511</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8597</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5517</v>
+        <v>3.7478</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2317</v>
+        <v>3.0875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.32</v>
+        <v>0.6603</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4399</v>
+        <v>3.7785</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7203</v>
+        <v>2.2743</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7196</v>
+        <v>1.5042</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7409</v>
+        <v>3.0586</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2993</v>
+        <v>3.0097</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4416</v>
+        <v>0.0489</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.301</v>
+        <v>0.7199</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2781</v>
+        <v>1.4554</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0003</v>
+        <v>1.9474</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6317</v>
+        <v>-0.3939</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4913</v>
+        <v>0.1126</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1404</v>
+        <v>-0.5065</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5196</v>
+        <v>-0.6105</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5196</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1673</v>
+        <v>3.6237</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4226</v>
+        <v>2.9359</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7447</v>
+        <v>0.6878</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5803</v>
+        <v>3.4961</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3121</v>
+        <v>3.0974</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2681</v>
+        <v>0.3987</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1252</v>
+        <v>4.7157</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5995</v>
+        <v>3.9052</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5256</v>
+        <v>0.8105</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4551</v>
+        <v>-1.2196</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7126</v>
+        <v>-0.8078</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2575</v>
+        <v>-0.4118</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8005</v>
+        <v>0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8008</v>
+        <v>2.3368</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2135</v>
+        <v>-0.8724</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7023</v>
+        <v>-0.443</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5111</v>
+        <v>-0.4294</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9834</v>
+        <v>3.1281</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3038</v>
+        <v>3.0989</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6796</v>
+        <v>0.0292</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4485</v>
+        <v>4.4651</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0417</v>
+        <v>1.7093</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4068</v>
+        <v>2.7558</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5424</v>
+        <v>4.8571</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7426</v>
+        <v>2.3605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7999000000000001</v>
+        <v>2.4966</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0939</v>
+        <v>-0.392</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7009</v>
+        <v>-0.6513</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3931</v>
+        <v>0.2592</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4007</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4651</v>
+        <v>0.1957</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8379</v>
+        <v>0.1892</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6272</v>
+        <v>0.0064</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7445</v>
+        <v>1.7332</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0577</v>
+        <v>0.3536</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8022</v>
+        <v>1.3796</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7075</v>
+        <v>2.6557</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8051</v>
+        <v>2.7725</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0975</v>
+        <v>-0.1168</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5032</v>
+        <v>1.6042</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6992</v>
+        <v>2.7711</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.196</v>
+        <v>-1.1669</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2043</v>
+        <v>1.0515</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1058</v>
+        <v>0.0014</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0985</v>
+        <v>1.0501</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0372</v>
+        <v>0.0512</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2402</v>
+        <v>0.4495</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2029</v>
+        <v>-0.3983</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="9">
@@ -1111,31 +1111,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5034</v>
+        <v>-0.5007</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4062</v>
+        <v>0.3673</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9096</v>
+        <v>-0.868</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5347</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5805</v>
+        <v>0.5477</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5017</v>
+        <v>0.5444</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3417</v>
+        <v>0.3823</v>
       </c>
       <c r="L10" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4298</v>
+        <v>-0.5315</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.9171</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3161</v>
+        <v>-1.1816</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0955</v>
+        <v>-0.1772</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2206</v>
+        <v>-1.0044</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2872</v>
+        <v>-0.9694</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2369</v>
+        <v>-2.0283</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9496</v>
+        <v>1.0589</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6224</v>
+        <v>-0.6148</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2956</v>
+        <v>-0.2971</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3268</v>
+        <v>-0.3177</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9143</v>
+        <v>-0.8451</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3163</v>
+        <v>-0.2616</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2919</v>
+        <v>0.2303</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0207</v>
+        <v>-0.0355</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8649</v>
+        <v>-0.5494</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3223</v>
+        <v>-0.2095</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5426</v>
+        <v>-0.3399</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.371</v>
+        <v>-1.1746</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1797</v>
+        <v>-1.3588</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8087</v>
+        <v>0.1842</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4805</v>
+        <v>-0.4435</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0335</v>
+        <v>1.0232</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5141</v>
+        <v>-1.4667</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.407</v>
+        <v>-0.2147</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9851</v>
+        <v>1.106</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3922</v>
+        <v>-1.3207</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0735</v>
+        <v>-0.2288</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0484</v>
+        <v>-0.0828</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.35</v>
+        <v>-0.2317</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8313</v>
+        <v>-0.3341</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4813</v>
+        <v>0.1024</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4832</v>
+        <v>-2.2336</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9032</v>
+        <v>-2.7349</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4199</v>
+        <v>0.5013</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8315</v>
+        <v>-1.8109</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1027</v>
+        <v>-2.0767</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.974</v>
+        <v>-1.9319</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.974</v>
+        <v>-1.9319</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1425</v>
+        <v>0.1211</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1287</v>
+        <v>-0.1447</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1485</v>
+        <v>0.3562</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0711</v>
+        <v>0.1707</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1855</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.8611</v>
+        <v>-2.3392</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2461</v>
+        <v>-2.6032</v>
       </c>
       <c r="F14" t="n">
-        <v>0.385</v>
+        <v>0.264</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.3619</v>
+        <v>-2.4021</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.799</v>
+        <v>-0.8771</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5628</v>
+        <v>-1.5251</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.1323</v>
+        <v>-1.0549</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1799</v>
+        <v>0.1847</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3122</v>
+        <v>-1.2396</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2296</v>
+        <v>-1.3473</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.979</v>
+        <v>-1.0618</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8397</v>
+        <v>-1.2418</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7735</v>
+        <v>-0.2436</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0662</v>
+        <v>-0.9982</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>24.1109</v>
+        <v>24.4208</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6746</v>
+        <v>14.3593</v>
       </c>
       <c r="F15" t="n">
-        <v>12.4361</v>
+        <v>10.0615</v>
       </c>
       <c r="G15" t="n">
-        <v>24.13280000000001</v>
+        <v>24.2636</v>
       </c>
       <c r="H15" t="n">
-        <v>16.1684</v>
+        <v>16.1256</v>
       </c>
       <c r="I15" t="n">
-        <v>7.9645</v>
+        <v>8.138000000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>23.5809</v>
+        <v>25.1042</v>
       </c>
       <c r="K15" t="n">
-        <v>19.1434</v>
+        <v>20.1574</v>
       </c>
       <c r="L15" t="n">
-        <v>4.437500000000001</v>
+        <v>4.946700000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5519000000000001</v>
+        <v>-0.8405999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.9753</v>
+        <v>-4.032</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5272</v>
+        <v>3.191400000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>3.001</v>
+        <v>2.9211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-19.0057</v>
+        <v>-18.5001</v>
       </c>
       <c r="R15" t="n">
-        <v>22.0064</v>
+        <v>21.421</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.5238</v>
+        <v>-3.1981</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4010999999999999</v>
+        <v>0.863</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.9248</v>
+        <v>-4.0613</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5007</v>
+        <v>0.4342999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>6.697900000000001</v>
+        <v>6.8921</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.197400000000001</v>
+        <v>-6.458</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8482</v>
+        <v>2.0154</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9574</v>
+        <v>1.1042</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8908</v>
+        <v>0.9112</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2222</v>
+        <v>1.2295</v>
       </c>
       <c r="H16" t="n">
-        <v>0.951</v>
+        <v>0.9637</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2796</v>
+        <v>1.3137</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2796</v>
+        <v>1.3137</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0574</v>
+        <v>-0.0842</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3286</v>
+        <v>-0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1743</v>
+        <v>0.0069</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3223</v>
+        <v>-0.2095</v>
       </c>
       <c r="U16" t="n">
-        <v>0.148</v>
+        <v>0.2164</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTIN CASTANEDA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0375</v>
+        <v>0.6079</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7922</v>
+        <v>0.6079</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7547</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2666</v>
+        <v>0.6079</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7118</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5548</v>
+        <v>0.6079</v>
       </c>
       <c r="J17" t="n">
-        <v>0.349</v>
+        <v>0.6079</v>
       </c>
       <c r="K17" t="n">
-        <v>0.867</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.518</v>
+        <v>0.6079</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6156</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5788</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0368</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0006</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4356</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4435</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1318</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6393</v>
+        <v>0.3497</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2995</v>
+        <v>1.1631</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6601</v>
+        <v>-0.8134</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6486</v>
+        <v>-0.6731</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6555</v>
+        <v>-0.6666</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0069</v>
+        <v>-0.0066</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0018</v>
+        <v>0.0334</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0018</v>
+        <v>0.0334</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6504</v>
+        <v>-0.7065</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6573</v>
+        <v>-0.7</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0069</v>
+        <v>-0.0066</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2196</v>
+        <v>-0.0171</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0979</v>
+        <v>-0.0914</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1217</v>
+        <v>0.0743</v>
       </c>
       <c r="V18" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1318</v>
+        <v>-1.1548</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>A. MARTIN CASTANEDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5999</v>
+        <v>-0.405</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5999</v>
+        <v>1.3417</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.7466</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5999</v>
+        <v>-2.2729</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.6614</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5999</v>
+        <v>-1.6115</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5999</v>
+        <v>0.5138</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.0162</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5999</v>
+        <v>-0.5024</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-2.7867</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.6776</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.1091</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.9474</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.0491</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.8016</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2476</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.1548</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1548</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. HERNANDEZ MARTIN</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1088</v>
+        <v>-0.4684</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1171</v>
+        <v>1.3137</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0083</v>
+        <v>-1.7821</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7216</v>
+        <v>-0.2945</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9372</v>
+        <v>-1.1032</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2156</v>
+        <v>0.8087</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6435999999999999</v>
+        <v>2.5515</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0418</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6018</v>
+        <v>1.9047</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3652</v>
+        <v>-2.846</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.979</v>
+        <v>-1.7499</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3862</v>
+        <v>-1.096</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2001</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8005</v>
+        <v>1.1684</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2129</v>
+        <v>-0.0055</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0401</v>
+        <v>0.4301</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1728</v>
+        <v>-0.4356</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1998</v>
+        <v>0.2795</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5999</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>C. HERNANDEZ MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5523</v>
+        <v>-0.4836</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1504</v>
+        <v>-0.2632</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7028</v>
+        <v>-0.2204</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3068</v>
+        <v>-0.7734</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1361</v>
+        <v>-0.9873</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8292</v>
+        <v>0.214</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3868</v>
+        <v>0.7068</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5071</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8797</v>
+        <v>0.6323</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6937</v>
+        <v>-1.4802</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6431</v>
+        <v>-1.0618</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0505</v>
+        <v>-0.4184</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8002</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2003</v>
+        <v>1.7526</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0452</v>
+        <v>-0.126</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4956</v>
+        <v>-0.2436</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5496</v>
+        <v>0.1177</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2598</v>
+        <v>1.2211</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3401</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6454</v>
+        <v>-2.2037</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5433</v>
+        <v>-0.9019</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1021</v>
+        <v>-1.3018</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2873</v>
+        <v>-4.9924</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6836</v>
+        <v>-1.5513</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6037</v>
+        <v>-3.4411</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0705</v>
+        <v>-3.0228</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0306</v>
+        <v>0.2592</v>
       </c>
       <c r="L22" t="n">
-        <v>0.04</v>
+        <v>-3.282</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3578</v>
+        <v>-1.9696</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.7141</v>
+        <v>-1.8105</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6437</v>
+        <v>-0.1591</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8002</v>
+        <v>2.1421</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8008</v>
+        <v>2.1421</v>
       </c>
       <c r="S22" t="n">
-        <v>1.202</v>
+        <v>0.8599</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4873</v>
+        <v>0.8999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2853</v>
+        <v>-0.0399</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3604</v>
+        <v>-0.2133</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.1006</v>
+        <v>1.2211</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2598</v>
+        <v>-1.4343</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9682</v>
+        <v>-2.6373</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2434</v>
+        <v>-1.4173</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2753</v>
+        <v>-1.22</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6621</v>
+        <v>-2.2464</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.427</v>
+        <v>-1.5896</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7648</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9543</v>
+        <v>1.2877</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0343</v>
+        <v>1.2472</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7078</v>
+        <v>-3.5341</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3927</v>
+        <v>-2.8368</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6849</v>
+        <v>-0.6973</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.2003</v>
+        <v>0.7789</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8002</v>
+        <v>2.7263</v>
       </c>
       <c r="S23" t="n">
-        <v>1.4262</v>
+        <v>0.1544</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7114</v>
+        <v>0.287</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7147</v>
+        <v>-0.1327</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5319</v>
+        <v>-1.3242</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.0447</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5319</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2063</v>
+        <v>-2.8008</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9461</v>
+        <v>-2.7209</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2601</v>
+        <v>-0.0799</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.9508</v>
+        <v>-1.6769</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4927</v>
+        <v>-2.4159</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4582</v>
+        <v>0.739</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1283</v>
+        <v>-0.8861</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2217</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.35</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8226</v>
+        <v>-0.7907</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7144</v>
+        <v>-1.4487</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1082</v>
+        <v>0.6579</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2006</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2006</v>
+        <v>0.7789</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2643</v>
+        <v>0.5888</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0177</v>
+        <v>0.1126</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2466</v>
+        <v>0.4762</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1918</v>
+        <v>-0.5443</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3915</v>
+        <v>-0.5443</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4286</v>
+        <v>-3.5781</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4153</v>
+        <v>-2.9596</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0133</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.756</v>
+        <v>-6.2805</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8067</v>
+        <v>-4.6112</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.5627</v>
+        <v>-1.6693</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1654</v>
+        <v>-3.2043</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1994</v>
+        <v>-2.3783</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.034</v>
+        <v>-0.826</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9214</v>
+        <v>-3.0762</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3927</v>
+        <v>-2.2328</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.8433</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.2003</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0006</v>
+        <v>-2.921</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8002</v>
+        <v>2.5316</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6126</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0.7236</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0325</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.8597</v>
+        <v>2.4421</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCIA</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.538</v>
+        <v>-4.0232</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7593</v>
+        <v>-1.9405</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7787</v>
+        <v>-2.0828</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.8145</v>
+        <v>-1.729</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.0907</v>
+        <v>0.8092</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2762</v>
+        <v>-2.5382</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3781</v>
+        <v>0.2644</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4981</v>
+        <v>2.2579</v>
       </c>
       <c r="L26" t="n">
-        <v>0.12</v>
+        <v>-1.9935</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.4365</v>
+        <v>-1.9934</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.5926</v>
+        <v>-1.4487</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1562</v>
+        <v>-0.5447</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2006</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.0009</v>
+        <v>-1.9474</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5228</v>
+        <v>-0.2358</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.2575</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0573</v>
+        <v>0.0217</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.1998</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>M. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.9177</v>
+        <v>-4.1075</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.2243</v>
+        <v>-2.4153</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6934</v>
+        <v>-1.6921</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.2917</v>
+        <v>-1.8989</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.5776</v>
+        <v>-2.1337</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.714</v>
+        <v>0.2348</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.4187</v>
+        <v>-0.3582</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.4703</v>
+        <v>-0.4798</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.9484</v>
+        <v>0.1216</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.873</v>
+        <v>-1.5407</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.1074</v>
+        <v>-1.6539</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.1132</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.4001</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R27" t="n">
-        <v>2.6007</v>
+        <v>0.7789</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.0665</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2043</v>
+        <v>-0.3572</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4211</v>
+        <v>0.2907</v>
       </c>
       <c r="V27" t="n">
-        <v>2.3995</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.3995</v>
+        <v>1.2211</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="28">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.8703</v>
+        <v>-5.0481</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.9866</v>
+        <v>-2.9732</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.8837</v>
+        <v>-2.0749</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.2488</v>
+        <v>-3.2629</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.2139</v>
+        <v>-2.1783</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.0349</v>
+        <v>-1.0847</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8307</v>
+        <v>1.033</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8288</v>
+        <v>1.0085</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0019</v>
+        <v>0.0244</v>
       </c>
       <c r="M28" t="n">
-        <v>-4.0796</v>
+        <v>-4.2959</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.0427</v>
+        <v>-3.1868</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.0368</v>
+        <v>-1.1091</v>
       </c>
       <c r="P28" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R28" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2719</v>
+        <v>0.9781</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3448</v>
+        <v>0.9654</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.0728</v>
+        <v>0.0127</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.0926</v>
+        <v>-0.0369</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.1606</v>
+        <v>-0.1032</v>
       </c>
       <c r="X28" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2671,67 +2671,67 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-24.1107</v>
+        <v>-22.7827</v>
       </c>
       <c r="E29" t="n">
-        <v>-12.436</v>
+        <v>-10.0613</v>
       </c>
       <c r="F29" t="n">
-        <v>-11.6745</v>
+        <v>-12.7212</v>
       </c>
       <c r="G29" t="n">
-        <v>-24.1327</v>
+        <v>-24.2635</v>
       </c>
       <c r="H29" t="n">
-        <v>-16.1684</v>
+        <v>-16.1256</v>
       </c>
       <c r="I29" t="n">
-        <v>-7.964499999999999</v>
+        <v>-8.138</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5520999999999987</v>
+        <v>0.8408000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>2.9751</v>
+        <v>4.031899999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>-3.527099999999999</v>
+        <v>-3.1914</v>
       </c>
       <c r="M29" t="n">
-        <v>-23.581</v>
+        <v>-25.1042</v>
       </c>
       <c r="N29" t="n">
-        <v>-19.1434</v>
+        <v>-20.1575</v>
       </c>
       <c r="O29" t="n">
-        <v>-4.4373</v>
+        <v>-4.9467</v>
       </c>
       <c r="P29" t="n">
-        <v>-3.0008</v>
+        <v>-2.921</v>
       </c>
       <c r="Q29" t="n">
-        <v>-22.0065</v>
+        <v>-21.4211</v>
       </c>
       <c r="R29" t="n">
-        <v>19.0052</v>
+        <v>18.4998</v>
       </c>
       <c r="S29" t="n">
-        <v>3.523499999999999</v>
+        <v>4.835999999999999</v>
       </c>
       <c r="T29" t="n">
-        <v>3.924900000000001</v>
+        <v>4.061</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.4012999999999999</v>
+        <v>0.7752000000000001</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.5008999999999997</v>
+        <v>-0.4342000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>6.197300000000001</v>
+        <v>6.4581</v>
       </c>
       <c r="X29" t="n">
-        <v>-6.6981</v>
+        <v>-6.891999999999999</v>
       </c>
     </row>
   </sheetData>
